--- a/platform_core_data/supplier-features/reissue/shared/reissue-flow/test_design/TestCases_ReissueFlow.xlsx
+++ b/platform_core_data/supplier-features/reissue/shared/reissue-flow/test_design/TestCases_ReissueFlow.xlsx
@@ -157,7 +157,7 @@
       </c>
       <c r="D2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Branch BRN265 has the Reissue checkbox enabled and a Sabre Staging credential selected under Auto Reissue credentials. A `Booked`, online-booked Sabre booking exists on that Branch.</t>
+          <t xml:space="preserve">Branch BRN265 has the Reissue checkbox enabled and the booking's Sabre Staging credential selected under Auto Reissue credentials. A reissuable booking (§0.8) exists on that Branch.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr" s="2">
@@ -219,7 +219,7 @@
       </c>
       <c r="D3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">A Branch with the Reissue checkbox **unticked**, carrying a `Booked` online Sabre booking. Changing a shared Branch's flag is master-data mutation — obtain a run-scoped grant and revert afterwards, or use a Branch already configured off.</t>
+          <t xml:space="preserve">A Branch with the Reissue checkbox **unticked**, carrying a booking that meets the other five D-14 conditions (§0.8). Changing a shared Branch's flag is master-data mutation — obtain a run-scoped grant and revert afterwards, or use a Branch already configured off.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr" s="2">
@@ -281,7 +281,7 @@
       </c>
       <c r="D4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">An Agency with the Reissue checkbox unticked, under a Reissue-enabled Branch.</t>
+          <t xml:space="preserve">An Agency with the Reissue checkbox unticked, under a Reissue-enabled Branch, carrying a booking that meets the other five D-14 conditions (§0.8).</t>
         </is>
       </c>
       <c r="E4" t="inlineStr" s="2">
@@ -715,7 +715,7 @@
       </c>
       <c r="D11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">All of: booking status `Booked`; booked online; booking **locked by the current user**; the owning organisation's Reissue flag on; the supplier a reissue-capable GDS.</t>
+          <t xml:space="preserve">All six D-14 conditions (§0.8): the owning organisation's Auto Reissue checkbox on; the booking's credential selected in that organisation's Auto Reissue credential picker; Status `Booked` **and** the status bar reads "Ticketed Document"; booked online; on Admin, booking **locked by the current user** (the Portal has no lock); the supplier a reissue-capable GDS.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr" s="2">
@@ -725,12 +725,12 @@
       </c>
       <c r="F11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. Open Admin → Booking → Search Booking → Flight tab, search by Booking Reference, open the booking. | 2. Lock the booking as the current user. | 3. Open the Itinerary and read the available actions on the booked flight.</t>
+          <t xml:space="preserve">1. Open the owning organisation's edit form; confirm Auto Reissue is ticked and the booking's credential is selected in the credential picker. Read only. | 2. Open Admin → Booking → Search Booking → Flight tab, search by Booking Reference, open the booking. | 3. Confirm Booking Information → Status reads `Booked` and the status bar reads "Ticketed Document". | 4. Lock the booking as the current user. | 5. Open the Itinerary and read the available actions on the booked flight. | 6. On the Portal, open the Agency booking's Itinerary (no lock exists there) and read the actions.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Reissue action is displayed and enabled. Selecting the flight starts the Eligibility phase.</t>
+          <t xml:space="preserve">The Reissue action is displayed and enabled on Admin once locked, and on the Portal without any lock. Selecting the flight starts the Eligibility phase.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr" s="2">
@@ -745,7 +745,7 @@
       </c>
       <c r="J11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Covers AC-02, AC-04, story §2 AC-1, edge case 1.4. **Discovery: EXECUTED.** Observed run-007 on both Admin and Portal.</t>
+          <t xml:space="preserve">Covers AC-02, AC-04, story §2 AC-1, edge case 1.4, D-14. **Discovery: EXECUTED.** Observed run-007 on both Admin and Portal. **Rev 2, 2026-10-01** — preconditions and steps state all six D-14 conditions; the credential-picker and "Ticketed Document" checks were added as steps 1 and 3. Step 6 added: the lock is **Admin-only**, the Portal has no lock (user, 2026-10-01).</t>
         </is>
       </c>
       <c r="K11" t="inlineStr" s="2">
@@ -767,17 +767,17 @@
       </c>
       <c r="B12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Reissue actions appear only while the booking is locked by the current user</t>
+          <t xml:space="preserve">On Admin, Reissue actions appear only while the booking is locked by the current user</t>
         </is>
       </c>
       <c r="C12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Verify the lock precondition from CL-3.</t>
+          <t xml:space="preserve">Verify the Admin lock precondition from CL-3 / D-14 condition 5. Admin only — the Portal has no lock.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">A reissuable booking, unlocked.</t>
+          <t xml:space="preserve">A booking that meets the other five D-14 conditions (§0.8), unlocked.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr" s="2">
@@ -787,7 +787,7 @@
       </c>
       <c r="F12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. Open the booking's Itinerary **without** locking it. Read the available actions. | 2. Lock the booking as the current user. Re-read the actions. | 3. Release the lock at the end.</t>
+          <t xml:space="preserve">1. On Admin, open the booking's Itinerary **without** locking it. Read the available actions. | 2. Lock the booking as the current user. Re-read the actions. | 3. Release the lock at the end.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr" s="2">
@@ -807,7 +807,7 @@
       </c>
       <c r="J12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Covers CL-3. **Discovery: EXECUTED.** Confirmed run-007 and recorded as correct by design — the withdrawn finding on lock-gated controls established this is intended, not a defect.</t>
+          <t xml:space="preserve">Covers CL-3, D-14 condition 5. **Discovery: EXECUTED.** Confirmed run-007 and recorded as correct by design — the withdrawn finding on lock-gated controls established this is intended, not a defect. **Rev 2, 2026-10-01** — scoped to Admin: the user confirmed the lock exists only on Admin; the Portal has no lock.</t>
         </is>
       </c>
       <c r="K12" t="inlineStr" s="2">
@@ -834,12 +834,12 @@
       </c>
       <c r="C13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Verify the credential rule of CL-1 — the single most contested behaviour in this story.</t>
+          <t xml:space="preserve">Verify the credential condition of D-14 — the Reissue button is not displayed when the booking's credential is not selected in the organisation's credential picker.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">An organisation whose Auto Reissue credential selection **excludes** the credential the booking was made on. Read as the lock holder.</t>
+          <t xml:space="preserve">An organisation whose Auto Reissue credential selection **excludes** the credential the booking was made on; the other five D-14 conditions hold (§0.8). Read as the lock holder.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr" s="2">
@@ -849,12 +849,12 @@
       </c>
       <c r="F13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. Note the booking's supplier credential. | 2. Set the organisation's Auto Reissue credential selection to exclude it. | 3. Lock the booking as the current user and open the Itinerary. | 4. Record whether the Reissue button is **shown**; if shown, click it and record the message. | 5. Restore the original credential selection.</t>
+          <t xml:space="preserve">1. Note the booking's supplier credential. | 2. Set the organisation's Auto Reissue credential selection to exclude it. | 3. Lock the booking as the current user and open the Itinerary. | 4. Read the Itinerary actions and record whether the Reissue button is displayed. | 5. Restore the original credential selection, and confirm the button is displayed again (control).</t>
         </is>
       </c>
       <c r="G13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">**Pending Confirmation.** CL-1 states the button is **shown** and the reissue refused on click with *"No credential for this booking is assigned to your organisation"*. **Observed run-007: the button is hidden and no message is ever shown** — reproduced with the prior run's exact setup, read as the lock holder, so the credential in use is not the cause. The application's behaviour changed after the prerequisite story was delivered and passed. Written to the story per requirement precedence; fixed when the product owner rules.</t>
+          <t xml:space="preserve">With the booking's credential **not** selected, the Reissue button is **not displayed** (`actionsDetails.canAutoReissue: false`), and no Reissue can be initiated. With the selection restored, the button is displayed.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr" s="2">
@@ -869,7 +869,7 @@
       </c>
       <c r="J13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Covers AC-02, AC-05, CL-1. **Discovery: PENDING CONFIRMATION** — **DS-2**. Evidence `evidence/cl1-*` (16 files). This case cannot be approved with a fixed expected result until DS-2 is settled.</t>
+          <t xml:space="preserve">Covers AC-02, AC-05, D-14 condition 2. **Discovery: EXECUTED** — observed run-007 exactly as expected: button hidden, `canAutoReissue: false` (`evidence/cl1-*`, 16 files). **Rev 2, 2026-10-01** — expected result fixed under **D-14**, which settles **DS-2**: Rev 1 was `Pending Confirmation` between CL-1's "shown, refused on click" and the observed "hidden". CL-1's click-time message is no longer a test target.</t>
         </is>
       </c>
       <c r="K13" t="inlineStr" s="2">
@@ -911,7 +911,7 @@
       </c>
       <c r="F14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. Open a `Booked`, online booking on an unlisted supplier, locked as the current user. | 2. Read the Itinerary actions. | 3. Repeat on a booking made through a listed supplier as the control.</t>
+          <t xml:space="preserve">1. Open a booking on an unlisted supplier that meets the other five D-14 conditions (§0.8), locked as the current user. | 2. Read the Itinerary actions. | 3. Repeat on a booking made through a listed supplier as the control.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr" s="2">
@@ -963,7 +963,7 @@
       </c>
       <c r="D15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">An offline or imported booking in `Booked` status on a reissue-capable supplier.</t>
+          <t xml:space="preserve">An offline or imported booking that meets the other five D-14 conditions (§0.8).</t>
         </is>
       </c>
       <c r="E15" t="inlineStr" s="2">
@@ -1015,32 +1015,32 @@
       </c>
       <c r="B16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">A booking not in Booked status does not offer Reissue</t>
+          <t xml:space="preserve">A booking that is not both Booked and "Ticketed Document" does not offer Reissue</t>
         </is>
       </c>
       <c r="C16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Verify the status precondition of CL-3, which corrects an earlier reading of the "Ticketed Document" bar.</t>
+          <t xml:space="preserve">Verify the status condition of D-14: Status `Booked` **and** the status bar "Ticketed Document", both required.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Bookings in statuses other than `Booked` — for example already `Reissued`, cancelled, or not yet ticketed.</t>
+          <t xml:space="preserve">Bookings that meet the other five D-14 conditions (§0.8) but fail the status condition — status other than `Booked` (for example already `Reissued`, or cancelled), or `Booked` with a status bar other than "Ticketed Document" (for example not yet ticketed).</t>
         </is>
       </c>
       <c r="E16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">`NDCEG-BR-F2609294YODAr` (now `Reissued`) as the negative; `NDCEG-BR-F260926PwYMR2` as the control.</t>
+          <t xml:space="preserve">`NDCEG-BR-F2609294YODAr` (now `Reissued`) as a negative; a `Booked` booking whose bar is not "Ticketed Document" to be supplied (**OQ-7**); `NDCEG-BR-F260926PwYMR2` as the control.</t>
         </is>
       </c>
       <c r="F16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. Open a booking whose status is `Reissued`, locked as the current user, and read the Itinerary actions. | 2. Repeat on a `Booked` booking as the control.</t>
+          <t xml:space="preserve">1. Open a booking whose status is `Reissued`, locked as the current user. Record Booking Information → Status and the status bar, and read the Itinerary actions. | 2. Repeat on a `Booked` booking whose status bar does **not** read "Ticketed Document". | 3. Repeat on a booking with Status `Booked` **and** the bar "Ticketed Document" as the control.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Reissue is offered only on `Booked`. The "Ticketed Document" bar label is **not** the condition. A booking already `Reissued` does not offer a further Reissue from the original.</t>
+          <t xml:space="preserve">Reissue is displayed only when Status is `Booked` **and** the status bar reads "Ticketed Document" (step 3). It is not displayed in steps 1 and 2. A booking already `Reissued` does not offer a further Reissue from the original.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr" s="2">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="J16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Covers AC-05, CL-3, edge case 7.7. **Discovery: PARTIAL** — the `Reissued` negative is observable on held data; other non-`Booked` statuses are not (**OQ-10**).</t>
+          <t xml:space="preserve">Covers AC-05, CL-3 as amended by D-14 condition 3, edge case 7.7. **Discovery: PARTIAL** — the `Reissued` negative and the positive control are observable on held data; a `Booked`-but-not-"Ticketed Document" booking and other non-`Booked` statuses are not (**OQ-7**, **OQ-10**). **Rev 2, 2026-10-01** — expected result changed under **D-14**: Rev 1 asserted the "Ticketed Document" bar was **not** the condition (CL-3 / `PO-24`); it now is, alongside Status `Booked`. Step 2 added for the new half of the condition.</t>
         </is>
       </c>
       <c r="K16" t="inlineStr" s="2">

--- a/platform_core_data/supplier-features/reissue/shared/reissue-flow/test_design/TestCases_ReissueFlow.xlsx
+++ b/platform_core_data/supplier-features/reissue/shared/reissue-flow/test_design/TestCases_ReissueFlow.xlsx
@@ -60,7 +60,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L128"/>
+  <dimension ref="A1:L149"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -192,7 +192,7 @@
       </c>
       <c r="K2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L2" t="inlineStr" s="2">
@@ -224,7 +224,7 @@
       </c>
       <c r="E3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">To be supplied — a Branch with Reissue off (**OQ-7**).</t>
+          <t xml:space="preserve">**No new booking is needed.** Take a booking already held on the organisation and switch that organisation's Auto Reissue checkbox **off** — run-006 did exactly this on AGN9780 (Agency side; the Branch side is the same technique on BRN265) and watched the button follow (`PO-25`: OFF hidden / ON shown / OFF hidden). Revert the checkbox afterwards.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr" s="2">
@@ -249,12 +249,12 @@
       </c>
       <c r="J3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Covers AC-01, AC-02, edge case 1.1. **Discovery: NOT TESTABLE.** Needs a Reissue-disabled Branch with a suitable booking — **OQ-7**. Declared Gap.</t>
+          <t xml:space="preserve">Covers AC-01, AC-02, edge case 1.1. **Discovery: NOT EXECUTED — reclassified 2026-10-04.** It was marked Not Testable for want of *"a Reissue-disabled Branch with a suitable booking"*, but no such booking is needed: the organisation's own checkbox is toggled on a booking already held, the technique `PO-25` records run-006 using. **The only precondition is authorisation** — switching a user-supplied organisation's checkbox is a configuration mutation, so it needs a run-scoped go-ahead and a revert, exactly as run-006 had. No longer blocked on **OQ-7**.</t>
         </is>
       </c>
       <c r="K3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L3" t="inlineStr" s="2">
@@ -286,7 +286,7 @@
       </c>
       <c r="E4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">To be supplied (**OQ-7**).</t>
+          <t xml:space="preserve">**No new booking is needed.** Take a booking already held on the organisation and switch that organisation's Auto Reissue checkbox **off** — run-006 did exactly this on AGN9780 and watched the button follow (`PO-25`: OFF hidden / ON shown / OFF hidden). Revert the checkbox afterwards.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr" s="2">
@@ -311,12 +311,12 @@
       </c>
       <c r="J4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Covers AC-01, edge case 1.2. **Discovery: NOT TESTABLE** — **OQ-7**. Declared Gap.</t>
+          <t xml:space="preserve">Covers AC-01, edge case 1.2. **Discovery: NOT EXECUTED — reclassified 2026-10-04.** `PO-25` records run-006 observing precisely this on AGN9780's booking, Portal side: the button followed the Agency checkbox OFF / ON / OFF. No new booking is required and **OQ-7** does not block it; a run-scoped grant to toggle the checkbox, and a revert, do apply.</t>
         </is>
       </c>
       <c r="K4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L4" t="inlineStr" s="2">
@@ -338,27 +338,27 @@
       </c>
       <c r="C5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Verify the precedence the story states between the two flags.</t>
+          <t xml:space="preserve">Verify that the flag of the organisation **that created the booking** governs, and that its parent's flag does not override it.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Branch Reissue **on**, Agency Reissue **off**, both on the same booking's ownership chain.</t>
+          <t xml:space="preserve">Branch Reissue **on**, Agency Reissue **off**, both on the same booking's ownership chain. The booking was created by the **Agency**. The other five D-14 conditions hold (§0.8).</t>
         </is>
       </c>
       <c r="E5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">To be supplied (**OQ-7**).</t>
+          <t xml:space="preserve">To be supplied (**OQ-7**) — a booking created by an Agency whose own Reissue flag is off, under a Branch whose flag is on.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. Set or find the Branch flag on and the Agency flag off. | 2. Open the Agency's booking and attempt to initiate Reissue.</t>
+          <t xml:space="preserve">1. Set or find the Branch flag on and the Agency flag off. | 2. Open the Agency's booking in the Itinerary and read whether the `Reissue` button is displayed.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">**Pending Confirmation.** The story's edge case 1.3 requires the feature be treated as unavailable for that Agency and initiation prevented. **Neither CL-1 nor the prerequisite run states this precedence, and the combination has never been tested** — see DS-6. Written to the story per the requirement-precedence rule; the expected result is fixed only when the product owner rules.</t>
+          <t xml:space="preserve">**The `Reissue` button is not displayed.** The Agency created the booking and its own Auto Reissue flag is off, so D-14 condition 1 fails and the button is hidden — there is no click-time refusal. The Branch's flag being on does **not** make the feature available to the Agency.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr" s="2">
@@ -373,12 +373,12 @@
       </c>
       <c r="J5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Covers AC-01, edge case 1.3. **Discovery: PENDING CONFIRMATION** — DS-6 open, and **OQ-7** for the data. Declared Gap on both counts.</t>
+          <t xml:space="preserve">Covers AC-01, edge case 1.3. **Expected result fixed 2026-10-04 — DS-6 settled by `PO-16`** (agency/branch ProjectContext; product-owner standing confirmed 2026-09-24) and by specification §5, which makes `canAutoReissue` true only when *the organisation that created the booking* has auto-reissue allowed. There is **no precedence between the two flags** — each organisation's own value applies to itself. **Discovery: NOT EXECUTED** — the combination has still never been run; it needs the **OQ-7** data. Declared Gap on the data only, no longer on the expected result.</t>
         </is>
       </c>
       <c r="K5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L5" t="inlineStr" s="2">
@@ -440,7 +440,7 @@
       </c>
       <c r="K6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L6" t="inlineStr" s="2">
@@ -502,7 +502,7 @@
       </c>
       <c r="K7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L7" t="inlineStr" s="2">
@@ -564,7 +564,7 @@
       </c>
       <c r="K8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L8" t="inlineStr" s="2">
@@ -626,7 +626,7 @@
       </c>
       <c r="K9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L9" t="inlineStr" s="2">
@@ -688,7 +688,7 @@
       </c>
       <c r="K10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L10" t="inlineStr" s="2">
@@ -750,7 +750,7 @@
       </c>
       <c r="K11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L11" t="inlineStr" s="2">
@@ -812,7 +812,7 @@
       </c>
       <c r="K12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L12" t="inlineStr" s="2">
@@ -874,7 +874,7 @@
       </c>
       <c r="K13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L13" t="inlineStr" s="2">
@@ -936,7 +936,7 @@
       </c>
       <c r="K14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L14" t="inlineStr" s="2">
@@ -998,7 +998,7 @@
       </c>
       <c r="K15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L15" t="inlineStr" s="2">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="K16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L16" t="inlineStr" s="2">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="K17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L17" t="inlineStr" s="2">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="K18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L18" t="inlineStr" s="2">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="K19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L19" t="inlineStr" s="2">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="K20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L20" t="inlineStr" s="2">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="K21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L21" t="inlineStr" s="2">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="K22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L22" t="inlineStr" s="2">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="K23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L23" t="inlineStr" s="2">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="K24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L24" t="inlineStr" s="2">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="K25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L25" t="inlineStr" s="2">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="K26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L26" t="inlineStr" s="2">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="K27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L27" t="inlineStr" s="2">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="K28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L28" t="inlineStr" s="2">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="K29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L29" t="inlineStr" s="2">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="K30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L30" t="inlineStr" s="2">
@@ -1990,7 +1990,7 @@
       </c>
       <c r="K31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L31" t="inlineStr" s="2">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="K32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L32" t="inlineStr" s="2">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="K33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L33" t="inlineStr" s="2">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L34" t="inlineStr" s="2">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="K35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L35" t="inlineStr" s="2">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="K36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L36" t="inlineStr" s="2">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="K37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L37" t="inlineStr" s="2">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="K38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L38" t="inlineStr" s="2">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="K39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L39" t="inlineStr" s="2">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="K40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L40" t="inlineStr" s="2">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="K41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L41" t="inlineStr" s="2">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="K42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L42" t="inlineStr" s="2">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="K43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L43" t="inlineStr" s="2">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="K44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L44" t="inlineStr" s="2">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="K45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L45" t="inlineStr" s="2">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="K46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L46" t="inlineStr" s="2">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="K47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L47" t="inlineStr" s="2">
@@ -3044,7 +3044,7 @@
       </c>
       <c r="K48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L48" t="inlineStr" s="2">
@@ -3106,7 +3106,7 @@
       </c>
       <c r="K49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L49" t="inlineStr" s="2">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="K50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L50" t="inlineStr" s="2">
@@ -3225,12 +3225,12 @@
       </c>
       <c r="J51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Covers AC-22, edge case 3.14. **Discovery: NOT TESTABLE** — a supplier reprice cannot be forced, **OQ-12**. Declared Gap. Observed opportunistically only.</t>
+          <t xml:space="preserve">Covers AC-22, edge case 3.14. **Discovery: NOT TESTABLE** — a supplier reprice cannot be forced, **OQ-12**. Declared Gap. Observed opportunistically only. **OQ-12 closed as D-15 (user, 2026-10-04): a supplier reprice cannot be forced — it is supplier behaviour the platform does not control.** This case is therefore **accepted as untested**, not awaiting an answer. **If the Price Changed popup ever appears during any execution, capture evidence on the spot** — screenshot, the before and after amounts, and the offer — it is the only route to ever specifying this behaviour.</t>
         </is>
       </c>
       <c r="K51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L51" t="inlineStr" s="2">
@@ -3292,7 +3292,7 @@
       </c>
       <c r="K52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L52" t="inlineStr" s="2">
@@ -3354,7 +3354,7 @@
       </c>
       <c r="K53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L53" t="inlineStr" s="2">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="K54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L54" t="inlineStr" s="2">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="K55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L55" t="inlineStr" s="2">
@@ -3540,7 +3540,7 @@
       </c>
       <c r="K56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L56" t="inlineStr" s="2">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="K57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L57" t="inlineStr" s="2">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="K58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L58" t="inlineStr" s="2">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="K59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L59" t="inlineStr" s="2">
@@ -3788,7 +3788,7 @@
       </c>
       <c r="K60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L60" t="inlineStr" s="2">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="K61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L61" t="inlineStr" s="2">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="K62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L62" t="inlineStr" s="2">
@@ -3974,7 +3974,7 @@
       </c>
       <c r="K63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L63" t="inlineStr" s="2">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="K64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L64" t="inlineStr" s="2">
@@ -4093,12 +4093,12 @@
       </c>
       <c r="J65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Covers edge case 4.6. **Discovery: NOT TESTABLE** — **OQ-12**. Declared Gap. Relevant context: run-007 confirmed "FARE HELD" on Review &amp; Pay is app-side only, not a supplier hold (D-12), so the price can move underneath it.</t>
+          <t xml:space="preserve">Covers edge case 4.6. **Discovery: NOT TESTABLE** — **OQ-12**. Declared Gap. Relevant context: run-007 confirmed "FARE HELD" on Review &amp; Pay is app-side only, not a supplier hold (D-12), so the price can move underneath it. **OQ-12 closed as D-15 (user, 2026-10-04): a supplier reprice cannot be forced — it is supplier behaviour the platform does not control.** This case is therefore **accepted as untested**, not awaiting an answer. **If the Price Changed popup ever appears during any execution, capture evidence on the spot** — screenshot, the before and after amounts, and the offer — it is the only route to ever specifying this behaviour.</t>
         </is>
       </c>
       <c r="K65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L65" t="inlineStr" s="2">
@@ -4155,12 +4155,12 @@
       </c>
       <c r="J66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Covers AC-22, story §4 AC-9, edge case 4.7. **Discovery: NOT TESTABLE** — a reprice cannot be forced; observed opportunistically only, and never seen. **OQ-12**. Declared Gap.</t>
+          <t xml:space="preserve">Covers AC-22, story §4 AC-9, edge case 4.7. **Discovery: NOT TESTABLE** — a reprice cannot be forced; observed opportunistically only, and never seen. **OQ-12**. Declared Gap. **OQ-12 closed as D-15 (user, 2026-10-04): a supplier reprice cannot be forced — it is supplier behaviour the platform does not control.** This case is therefore **accepted as untested**, not awaiting an answer. **If the Price Changed popup ever appears during any execution, capture evidence on the spot** — screenshot, the before and after amounts, and the offer — it is the only route to ever specifying this behaviour.</t>
         </is>
       </c>
       <c r="K66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L66" t="inlineStr" s="2">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="J67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Covers AC-22, edge case 4.7. **Discovery: NOT TESTABLE** — **OQ-12**. Declared Gap.</t>
+          <t xml:space="preserve">Covers AC-22, edge case 4.7. **Discovery: NOT TESTABLE** — **OQ-12**. Declared Gap. **OQ-12 closed as D-15 (user, 2026-10-04): a supplier reprice cannot be forced — it is supplier behaviour the platform does not control.** This case is therefore **accepted as untested**, not awaiting an answer. **If the Price Changed popup ever appears during any execution, capture evidence on the spot** — screenshot, the before and after amounts, and the offer — it is the only route to ever specifying this behaviour.</t>
         </is>
       </c>
       <c r="K67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L67" t="inlineStr" s="2">
@@ -4279,12 +4279,12 @@
       </c>
       <c r="J68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Covers edge case 4.9. **Discovery: NOT TESTABLE** — **OQ-12**. Declared Gap.</t>
+          <t xml:space="preserve">Covers edge case 4.9. **Discovery: NOT TESTABLE** — **OQ-12**. Declared Gap. **OQ-12 closed as D-15 (user, 2026-10-04): a supplier reprice cannot be forced — it is supplier behaviour the platform does not control.** This case is therefore **accepted as untested**, not awaiting an answer. **If the Price Changed popup ever appears during any execution, capture evidence on the spot** — screenshot, the before and after amounts, and the offer — it is the only route to ever specifying this behaviour.</t>
         </is>
       </c>
       <c r="K68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L68" t="inlineStr" s="2">
@@ -4341,12 +4341,12 @@
       </c>
       <c r="J69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Covers edge case 4.8. **Discovery: NOT TESTABLE** — **OQ-12**, and requires an offer known not to support Reprice. Declared Gap.</t>
+          <t xml:space="preserve">Covers edge case 4.8. **Discovery: NOT TESTABLE** — **OQ-12**, and requires an offer known not to support Reprice. Declared Gap. **OQ-12 closed as D-15 (user, 2026-10-04): a supplier reprice cannot be forced — it is supplier behaviour the platform does not control.** This case is therefore **accepted as untested**, not awaiting an answer. **If the Price Changed popup ever appears during any execution, capture evidence on the spot** — screenshot, the before and after amounts, and the offer — it is the only route to ever specifying this behaviour.</t>
         </is>
       </c>
       <c r="K69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L69" t="inlineStr" s="2">
@@ -4408,7 +4408,7 @@
       </c>
       <c r="K70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L70" t="inlineStr" s="2">
@@ -4470,7 +4470,7 @@
       </c>
       <c r="K71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L71" t="inlineStr" s="2">
@@ -4532,7 +4532,7 @@
       </c>
       <c r="K72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L72" t="inlineStr" s="2">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="K73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L73" t="inlineStr" s="2">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="K74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L74" t="inlineStr" s="2">
@@ -4718,7 +4718,7 @@
       </c>
       <c r="K75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L75" t="inlineStr" s="2">
@@ -4780,7 +4780,7 @@
       </c>
       <c r="K76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L76" t="inlineStr" s="2">
@@ -4842,7 +4842,7 @@
       </c>
       <c r="K77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L77" t="inlineStr" s="2">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="K78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L78" t="inlineStr" s="2">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="K79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L79" t="inlineStr" s="2">
@@ -5028,7 +5028,7 @@
       </c>
       <c r="K80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L80" t="inlineStr" s="2">
@@ -5090,7 +5090,7 @@
       </c>
       <c r="K81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L81" t="inlineStr" s="2">
@@ -5152,7 +5152,7 @@
       </c>
       <c r="K82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L82" t="inlineStr" s="2">
@@ -5214,7 +5214,7 @@
       </c>
       <c r="K83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L83" t="inlineStr" s="2">
@@ -5276,7 +5276,7 @@
       </c>
       <c r="K84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L84" t="inlineStr" s="2">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="K85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L85" t="inlineStr" s="2">
@@ -5400,7 +5400,7 @@
       </c>
       <c r="K86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L86" t="inlineStr" s="2">
@@ -5462,7 +5462,7 @@
       </c>
       <c r="K87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L87" t="inlineStr" s="2">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="K88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L88" t="inlineStr" s="2">
@@ -5586,7 +5586,7 @@
       </c>
       <c r="K89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L89" t="inlineStr" s="2">
@@ -5648,7 +5648,7 @@
       </c>
       <c r="K90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L90" t="inlineStr" s="2">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="K91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L91" t="inlineStr" s="2">
@@ -5772,7 +5772,7 @@
       </c>
       <c r="K92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L92" t="inlineStr" s="2">
@@ -5834,7 +5834,7 @@
       </c>
       <c r="K93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L93" t="inlineStr" s="2">
@@ -5896,7 +5896,7 @@
       </c>
       <c r="K94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L94" t="inlineStr" s="2">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="K95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L95" t="inlineStr" s="2">
@@ -6020,7 +6020,7 @@
       </c>
       <c r="K96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L96" t="inlineStr" s="2">
@@ -6082,7 +6082,7 @@
       </c>
       <c r="K97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L97" t="inlineStr" s="2">
@@ -6144,7 +6144,7 @@
       </c>
       <c r="K98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L98" t="inlineStr" s="2">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="K99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L99" t="inlineStr" s="2">
@@ -6268,7 +6268,7 @@
       </c>
       <c r="K100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L100" t="inlineStr" s="2">
@@ -6330,7 +6330,7 @@
       </c>
       <c r="K101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L101" t="inlineStr" s="2">
@@ -6392,7 +6392,7 @@
       </c>
       <c r="K102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L102" t="inlineStr" s="2">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="K103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L103" t="inlineStr" s="2">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="K104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L104" t="inlineStr" s="2">
@@ -6578,7 +6578,7 @@
       </c>
       <c r="K105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L105" t="inlineStr" s="2">
@@ -6640,7 +6640,7 @@
       </c>
       <c r="K106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L106" t="inlineStr" s="2">
@@ -6702,7 +6702,7 @@
       </c>
       <c r="K107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L107" t="inlineStr" s="2">
@@ -6764,7 +6764,7 @@
       </c>
       <c r="K108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L108" t="inlineStr" s="2">
@@ -6826,7 +6826,7 @@
       </c>
       <c r="K109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L109" t="inlineStr" s="2">
@@ -6888,7 +6888,7 @@
       </c>
       <c r="K110" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L110" t="inlineStr" s="2">
@@ -6950,7 +6950,7 @@
       </c>
       <c r="K111" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L111" t="inlineStr" s="2">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="K112" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L112" t="inlineStr" s="2">
@@ -7074,7 +7074,7 @@
       </c>
       <c r="K113" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L113" t="inlineStr" s="2">
@@ -7136,7 +7136,7 @@
       </c>
       <c r="K114" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L114" t="inlineStr" s="2">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="K115" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L115" t="inlineStr" s="2">
@@ -7260,7 +7260,7 @@
       </c>
       <c r="K116" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L116" t="inlineStr" s="2">
@@ -7322,7 +7322,7 @@
       </c>
       <c r="K117" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L117" t="inlineStr" s="2">
@@ -7384,7 +7384,7 @@
       </c>
       <c r="K118" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L118" t="inlineStr" s="2">
@@ -7446,7 +7446,7 @@
       </c>
       <c r="K119" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L119" t="inlineStr" s="2">
@@ -7508,7 +7508,7 @@
       </c>
       <c r="K120" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L120" t="inlineStr" s="2">
@@ -7570,7 +7570,7 @@
       </c>
       <c r="K121" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L121" t="inlineStr" s="2">
@@ -7632,7 +7632,7 @@
       </c>
       <c r="K122" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L122" t="inlineStr" s="2">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="K123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L123" t="inlineStr" s="2">
@@ -7756,7 +7756,7 @@
       </c>
       <c r="K124" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L124" t="inlineStr" s="2">
@@ -7818,7 +7818,7 @@
       </c>
       <c r="K125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L125" t="inlineStr" s="2">
@@ -7880,7 +7880,7 @@
       </c>
       <c r="K126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L126" t="inlineStr" s="2">
@@ -7942,7 +7942,7 @@
       </c>
       <c r="K127" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L127" t="inlineStr" s="2">
@@ -8004,10 +8004,1312 @@
       </c>
       <c r="K128" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Approved</t>
         </is>
       </c>
       <c r="L128" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">TC-RFLOW-128</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">An inactive airport is not offered in the widget's Origin field</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Verify the Origin autocomplete excludes airports whose administration status is Inactive.</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The Reissue flight widget open on a reissuable booking (§0.8). A known airport is set to **Inactive** in administration before the widget is opened.</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">One airport set Inactive in administration, identified by IATA code and by city name. One active control airport, to prove the field itself is working.</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. Set the chosen airport to Inactive in administration. Record its code and name. | 2. Open a reissuable booking, initiate Auto Reissue and continue to Search/Re-shop. | 3. In the widget's **Origin** field, type the inactive airport's IATA code. Read the suggestion list. | 4. Clear the field and type the inactive airport's **city or airport name**. Read the suggestion list. | 5. Type the active control airport's code and confirm it is offered.</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The inactive airport is **absent** from the Origin suggestion list by code and by name. The list is not empty and not broken — the active control airport is offered normally. No error is shown; the inactive airport simply does not exist as far as the widget is concerned.</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Atomic, Negative, Validation, Reference-Data</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Added at review 2026-10-04 (user); covers no story AC — the story does not mention airport status. **Discovery: NOT EXECUTED** — the widget's autocomplete was exercised in run-007 but never against an inactive airport. Runnable once an airport can be deactivated in the test environment; if administration access to the airport status flag is not held, this becomes a Declared Gap.</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Approved</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">TC-RFLOW-129</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">An inactive airport is not offered in the widget's Destination field</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Verify the Destination autocomplete applies the same exclusion as Origin.</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">As TC-RFLOW-128. The same airport is Inactive.</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The same inactive airport and active control airport as TC-RFLOW-128.</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. With the widget open, type the inactive airport's IATA code into the **Destination** field. Read the suggestion list. | 2. Clear the field and type its city or airport name. Read the suggestion list. | 3. Type the active control airport's code into Destination and confirm it is offered.</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The inactive airport is absent from the Destination suggestion list by code and by name. The active control airport is offered normally. Origin and Destination apply the same rule — the exclusion is not implemented on one field only.</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Atomic, Negative, Validation, Reference-Data</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Added at review 2026-10-04 (user). Deliberately separate from TC-RFLOW-128: a one-sided implementation is a realistic defect and a combined case would hide which field failed. **Discovery: NOT EXECUTED** — runnable under the same conditions as TC-RFLOW-128.</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Approved</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">TC-RFLOW-130</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">An airport deactivated while the widget is open is not accepted on submission</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Verify airport status is enforced at search time, not only when the suggestion list was first loaded.</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The widget open with an **active** airport selected as Origin or Destination. Administration access to change that airport's status in a second session.</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">An airport that is Active when the widget opens and is set Inactive before the search is submitted.</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. Open the widget and select the airport while it is still Active. | 2. Without reloading the widget, set that airport to **Inactive** in administration. | 3. Return to the widget and submit the search.</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The search is **not** performed against the now-inactive airport. The attempt is refused with a clear message naming the problem, and the user can correct the criteria. No Reissue transaction is created, and no results are returned for an airport that is no longer active.</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Atomic, Negative, Validation, Reference-Data, Race</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Added at review 2026-10-04 (user). The analogue of TC-RFLOW-018 (stale eligibility revalidated before Search) and TC-RFLOW-057 (wallet balance revalidated before payment) — a list cached when the widget opened is not authority at submission. **Discovery: NOT EXECUTED** — requires administration access concurrent with an open widget.</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Approved</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">TC-RFLOW-131</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">An inactive airport cannot be forced into the widget by a pasted code</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Verify the exclusion is enforced on submission, not only by hiding the entry in the suggestion list.</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The widget open. One airport Inactive in administration.</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The inactive airport's IATA code, pasted rather than selected from the list.</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. Paste the inactive airport's exact IATA code into Origin rather than choosing it from the suggestion list, and attempt to submit. | 2. Where the widget accepts a free-typed code without a list selection, attempt the search. | 3. Observe the search request and its response.</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The search is refused. An inactive airport is rejected on submission regardless of how it entered the field — hiding it from the suggestion list is not the only control. The refusal is a clear message, never a silent empty result set that reads as "no flights available".</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Atomic, Negative, Validation, Reference-Data</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Added at review 2026-10-04 (user). The distinction matters for the executor: an empty result set and a refusal look alike on screen but are different defects — TC-RFLOW-034 owns the genuine "no flights available" message. **Discovery: NOT EXECUTED.**</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Approved</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">TC-RFLOW-132</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Reactivating an airport restores it to the widget</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Verify the exclusion follows the airport's current flag rather than dropping it permanently.</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The airport used in TC-RFLOW-128 is currently Inactive and confirmed absent from the widget.</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The same airport, set back to **Active**.</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. Confirm the airport is absent from the widget's Origin and Destination suggestions. | 2. Set the airport back to **Active** in administration. | 3. Open the Reissue flight widget afresh and type the airport's code into Origin, then Destination. | 4. Select it and run a valid search.</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The airport is offered again in both fields, and a search using it is accepted and returns results normally. The widget reflects the airport's **current** status; deactivation is reversible and leaves no residue.</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P3</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Atomic, Positive, Reference-Data</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Added at review 2026-10-04 (user). Also the teardown for TC-RFLOW-128 to TC-RFLOW-131 — run it last so the environment is left as it was found. **Discovery: NOT EXECUTED.**</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Approved</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">TC-RFLOW-133</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Review &amp; Pay displays a FARE HELD countdown starting at 15 minutes</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Verify the countdown is present on Review &amp; Pay and begins at 15 minutes.</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">A reissuable booking (§0.8) carried through Eligibility, Search and offer selection to Review &amp; Pay.</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The clean reissue booking (§0.7).</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. Select an offer and open Review &amp; Pay. Note the wall-clock time at which the screen renders. | 2. Read the FARE HELD countdown's initial value immediately on render.</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">A FARE HELD countdown is displayed on Review &amp; Pay and its initial value is **15 minutes** (allowing for the seconds elapsed between the hold being issued and the screen rendering). It is legible and identifiable as the fare hold, not mistakable for another duration on the screen.</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Atomic, Positive, Smoke</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Added at review 2026-10-04 (user); covers no story AC. **Discovery: PARTIAL** — the countdown itself was observed in run-007 (`reissue-mapping` inventory V12, hold token `flight-token` JWT `exp`), but its starting value was never asserted against 15 minutes.</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Approved</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">TC-RFLOW-134</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The countdown decrements continuously and stays visible for the whole of Review &amp; Pay</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Verify the countdown is a live clock, not a static label, and does not disappear while the screen is in use.</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Review &amp; Pay open with the countdown showing.</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The clean reissue booking (§0.7).</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. Read the countdown, wait 60 seconds without interacting, and read it again. | 2. Scroll the screen, expand and collapse the fare breakdown, and select a payment method. Read the countdown after each. | 3. Remain on the screen and confirm the countdown continues to decrement toward zero.</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The countdown decrements in real time — roughly one minute lost per minute elapsed — and remains visible and correct through scrolling, breakdown expansion and payment-method selection. Interacting with the screen neither hides it nor restarts it.</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Atomic, Positive</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Added at review 2026-10-04 (user). A countdown that silently stops is worse than none: the executor must confirm it tracks real elapsed time, not that it merely rendered once. **Discovery: NOT EXECUTED** — runnable on held data.</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Approved</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">TC-RFLOW-135</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">An expired countdown makes the offer unavailable and payment is refused</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Verify the confirmed rule — at zero, the offer is no longer available.</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Review &amp; Pay open. **Read §0.4 before executing: this case never clicks Pay to completion.** The attempt is made only to confirm it is refused; if the screen's behaviour at expiry is to disable or remove the control, no click occurs at all.</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The clean reissue booking (§0.7). Approximately 15 minutes of elapsed time on the screen.</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. Reach Review &amp; Pay with a selected offer and note the countdown. | 2. Remain on the screen without paying until the countdown reaches **00:00**. | 3. Read what the screen does at zero — the countdown's final state, any message, and the state of the payment controls. | 4. If the payment control is still enabled, attempt to continue and read the response. Stop at the refusal; do not complete a payment.</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">At zero the offer is **no longer available**. The screen says so clearly, and payment against the expired offer cannot proceed — whether by the control being disabled, by the attempt being refused, or by the user being returned to Search. No charge is taken, no Reissue transaction is created against the expired offer, and the booking is left exactly as it was.</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Atomic, Negative, Validation</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Added at review 2026-10-04 (user). The expiry rule was confirmed by the user on 2026-10-04 — **the offer will not be available**. The precise presentation at zero (message wording, whether the user is returned to Search automatically) was not specified; the executor records what the screen actually does and the case passes on the substance, not the wording. **Discovery: NOT EXECUTED** — never held to expiry in run-007.</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Approved</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">TC-RFLOW-136</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Reloading or re-opening Review &amp; Pay does not restart the 15 minutes</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Verify the hold belongs to the offer, not to the page, so a refresh cannot extend it.</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Review &amp; Pay open with the countdown part-way down — roughly 5 minutes elapsed.</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The clean reissue booking (§0.7).</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. Reach Review &amp; Pay and let the countdown run down by about 5 minutes. Note the value. | 2. Refresh the browser on Review &amp; Pay. Read the countdown. | 3. Navigate back to the flight results and re-open the **same** offer. Read the countdown.</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">After a refresh, and after re-opening the same offer, the countdown continues from where the real elapsed time puts it — it does **not** return to 15 minutes. The fare hold cannot be extended by reloading. If re-selecting the offer legitimately issues a **new** hold, the screen makes that explicit rather than appearing to have gained time on the old one.</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Atomic, Negative, Validation</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Added at review 2026-10-04 (user). A refresh-resets-the-timer defect lets the fare be held indefinitely against the supplier's quote. The second branch of the Expected Result is deliberate: a new hold is acceptable, an apparently extended old one is not. **Discovery: NOT EXECUTED.**</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Approved</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">TC-RFLOW-137</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">An expired offer permits a clean return to Search with the Reissue context intact</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Verify expiry is recoverable — the user can search again without restarting the whole Reissue.</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">TC-RFLOW-135 executed; the countdown has reached zero and the offer is unavailable.</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The clean reissue booking (§0.7).</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. From the expired Review &amp; Pay, return to Search/Re-shop by whatever route the screen offers. | 2. Read the widget's criteria, and the selected passengers and journey. | 3. Run the search again, select an offer and reach Review &amp; Pay.</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The user returns to Search with the Reissue context intact — the same booking, the same passenger and journey selection, and the widget's criteria preserved. A fresh search is accepted, a new offer can be selected, and a **new** 15-minute hold starts. The expiry cost the offer, not the Reissue attempt; nothing forces the user back to the Itinerary to start again.</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">End-to-End, Positive, Recovery</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Added at review 2026-10-04 (user). Pairs with TC-RFLOW-035 and TC-RFLOW-038, which hold the same principle for a failed search and for changed criteria. **Discovery: NOT EXECUTED.**</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Approved</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">TC-RFLOW-138</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The 15-minute hold never outlasts the supplier's own offer validity</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Verify the app's countdown and the supplier's `validUntil` do not disagree in the dangerous direction.</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Review &amp; Pay open, with access to the supplier's offer response for the selected offer.</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">An offer whose supplier `validUntil` is **shorter** than 15 minutes — **never observed**. Declared Gap, concern **CN-21**.</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. Select an offer and capture the supplier response's `validUntil` for it. | 2. Open Review &amp; Pay and read the FARE HELD countdown's start value. | 3. Compare the two expiry instants against the same clock. | 4. Where the supplier's validity is the shorter, hold the screen past the supplier's expiry but before the app's, and read what the screen shows.</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The displayed hold **never outlasts** the supplier's offer validity. An offer already expired at the supplier is never still displayed as held, and payment against it is refused by the same rule as TC-RFLOW-135. Where the app's 15 minutes is the shorter of the two, the app's own expiry governs and the behaviour is TC-RFLOW-135's.</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Atomic, Negative, Integration</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Added at review 2026-10-04 (user). **This is the behavioural half of concern `CN-21`**; `reissue-mapping`'s `TC-RMAPF-031` and `TC-RMAPX-060` cover the countdown as a displayed value. The one observed Sabre scenario quoted `validUntil` of 20 minutes against the app's 15, which is the safe direction — the unsafe one has never been seen. **Discovery: NOT TESTABLE** — no offer with a sub-15-minute supplier validity is held. Declared Gap, **CN-21**.</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Approved</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">TC-RFLOW-139</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">A payment submitted as the countdown expires is not charged against an unavailable offer</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Verify the expiry is enforced at the server on submission, not only by the on-screen clock.</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Review &amp; Pay open with a payment method selected and the countdown within seconds of zero. **A human performs any payment action (§0.4, D-1); the agent reports the flight and amount and stops.**</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The clean reissue booking (§0.7).</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. Reach Review &amp; Pay, select a payment method and let the countdown run to the last few seconds. | 2. The human submits payment at the moment the countdown reaches zero. | 3. Read the outcome: the response, the booking's status, the wallet balance and whether a Reissue transaction was created.</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Either the payment is accepted because it was genuinely received before expiry and the Reissue completes normally, or it is refused because the offer had expired — and in the refused case **nothing is charged**: the wallet balance is unchanged, no new Booking Reference or Order ID exists, the original booking is not marked Reissued, and no orphan Reissue transaction is left behind. What must never happen is a charge against an offer the supplier no longer honours.</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">End-to-End, Negative, Race, Integration</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Added at review 2026-10-04 (user). The expiry equivalent of TC-RFLOW-057 (wallet revalidated immediately before payment) and TC-RFLOW-079 (a duplicate Exchange is not processed twice). **Discovery: NOT TESTABLE** — requires a human-performed payment timed to the second against a live supplier, which run-007 never attempted. Declared Gap; raise with the product owner whether this is acceptable to verify in a staging environment at all.</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Approved</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">TC-RFLOW-140</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The results screen labels the payable amount "Due Now"</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Verify the payable difference carries its agreed label on the flight-results screen.</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">A Re-shop search run on a reissuable booking (§0.8), returning at least one selectable offer.</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The clean reissue booking (§0.7).</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. Run a Re-shop search and read the results. | 2. Read the label attached to the amount the user would pay on each result. | 3. Compare it to the amount shown for the same offer on Review &amp; Pay after selection.</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The payable amount is labelled **"Due Now"**, and the value under that label is the **difference payable**, never the replacement flight's total price. The same offer carries the same figure under the same label on Review &amp; Pay.</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Atomic, Positive, Labelling</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Added 2026-10-04 from **DS-7 item 2**, confirmed by the user to exist on screen. Covers no story AC — the story never names this field. Complements TC-RFLOW-041, which asserts the *value* is the difference, and TC-RFLOW-053, which asserts its *position* on Review &amp; Pay; neither asserts the **label**. **Discovery: NOT EXECUTED** — runnable on held data. Related finding: `reissue-flow` FINDING on reissue columns carrying the difference under a fare label — the label question is live on this feature.</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Approved</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">TC-RFLOW-141</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">"Due Now" on Review &amp; Pay is Supplier Penalty + WT Change Fee + fare difference</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Verify the payable amount carries its label and equals its own stated composition.</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Review &amp; Pay open on a selected offer, with the fare breakdown visible.</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The clean reissue booking (§0.7). Agency exchange fee 50 or Branch 100, per passenger (D-7, D-11).</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. Open Review &amp; Pay on a selected offer. | 2. Read the amount labelled **"Due Now"** and its position. | 3. Read the fare difference, the supplier penalty and the WT change fee from the breakdown. | 4. Add the three and compare the sum to "Due Now".</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The payable amount is labelled **"Due Now"**, sits in the right-top area, and equals **fare difference + supplier penalty + WT change fee** to the last decimal. It is never the replacement flight's total price, and it never disagrees with the breakdown beneath it.</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Atomic, Positive, Calculation, Labelling</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Added 2026-10-04 from **DS-7 item 2**, confirmed by the user. The composition comes from the workflow diagram's `Sum Total Fees → Supplier+WT+Diff → Display Due Now`. Covers no story AC. Extends TC-RFLOW-053 (position) and TC-RFLOW-046 (breakdown components) with the **arithmetic between them**, which nothing asserted. **Discovery: NOT EXECUTED** — runnable on held data. **A supplier penalty has never been observed at anything but zero**, so step 3's penalty may be 0 on the held bookings; that does not invalidate the sum.</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Approved</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">TC-RFLOW-142</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Terms &amp; Conditions are displayed on Review &amp; Pay</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Verify the T&amp;C control exists on the payment screen.</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Review &amp; Pay open on a selected offer.</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The clean reissue booking (§0.7).</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. Open Review &amp; Pay and locate the Terms &amp; Conditions control. | 2. Read its label, its position relative to the payment action, and whether it is ticked by default.</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">A Terms &amp; Conditions control is displayed on Review &amp; Pay, before the `Confirm &amp; Charge` action, and is **not pre-accepted**. The user has to act on it deliberately.</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Atomic, Positive, Smoke</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Added 2026-10-04 from **DS-7 item 1**, confirmed by the user to exist. **Covers `AC-37`**, added to the story on 2026-10-04 on the user's instruction — when this case was written the story had no AC for it at all, and *"T&amp;C"* and *"Terms"* appeared nowhere in it. The control comes from the End-to-End Workflow documents, both diagram forms of which show `… → Accept T&amp;C → Confirm &amp; Charge` as a gate on the payment path. **If the control is pre-ticked, that is the finding** — a pre-accepted agreement is not an acceptance. **Discovery: NOT EXECUTED** — never looked for in any run.</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Approved</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">TC-RFLOW-143</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Payment cannot proceed until Terms &amp; Conditions are accepted</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Verify T&amp;C acceptance is a required gate, not a decoration.</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Review &amp; Pay open, a payment method selected, Terms &amp; Conditions **not** accepted. **Read §0.4: this case never completes a payment.** It establishes that the action is refused, and stops there.</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The clean reissue booking (§0.7).</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. Reach Review &amp; Pay, select a payment method, and leave Terms &amp; Conditions unaccepted. | 2. Read the state of the `Confirm &amp; Charge` action — enabled or disabled. | 3. If it is enabled, attempt to continue and read the response. **Stop at the refusal; do not complete a payment.** | 4. Accept Terms &amp; Conditions and read the state of the action again. **Do not continue past this point.**</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">With Terms &amp; Conditions unaccepted, payment **cannot proceed** — the action is disabled, or the attempt is refused with a message naming the unaccepted terms. No charge is taken and no Reissue transaction is created. Once accepted, the action becomes available.</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Atomic, Negative, Validation</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Added 2026-10-04 from **DS-7 item 1**, confirmed by the user. **Covers `AC-37`**, added to the story the same day — the AC exists *because* this gap was found. **This is the case that matters of the four** — both diagram forms place `Accept T&amp;C` directly before `Confirm &amp; Charge`, making it a mandatory gate on the money path. If payment proceeds without acceptance, the gate does not exist. **Discovery: NOT EXECUTED** — runnable on held data, and it stops before payment, so it needs no human-performed step.</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Approved</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">TC-RFLOW-144</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The Terms &amp; Conditions content is reachable and readable</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Verify the user can read what they are being asked to accept.</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Review &amp; Pay open with the Terms &amp; Conditions control visible.</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The clean reissue booking (§0.7).</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. Open the Terms &amp; Conditions from its link, modal or expander. | 2. Read whether content is returned, and whether it is reissue-relevant or generic booking terms. | 3. Close it and confirm the Review &amp; Pay state — the selected offer, the payment method and the amount — is unchanged.</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The terms open and display content. Opening and closing them does not disturb the selected offer, the payment method, the amount, or the fare hold. An acceptance control that leads to nothing readable is a defect.</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Atomic, Positive</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Added 2026-10-04 from **DS-7 item 1**. **Covers `AC-37`** (story §4.9, added 2026-10-04). Deliberately does not assert the *wording* of the terms — no approved text was supplied, and asserting content against nothing is the TC-RFLOW-092 problem. If the terms are expected to be reissue-specific rather than the standard booking terms, that is a product question to settle before this case is executed. **Discovery: NOT EXECUTED.**</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Approved</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">TC-RFLOW-145</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Terms &amp; Conditions acceptance does not carry over to a new offer</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Verify acceptance belongs to the transaction being agreed, not to the session.</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Review &amp; Pay reached with Terms &amp; Conditions accepted, payment not made.</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The clean reissue booking (§0.7); at least two selectable offers from one search.</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. Reach Review &amp; Pay on the first offer and accept Terms &amp; Conditions. Do not pay. | 2. Return to the flight results and select a **different** offer. | 3. On the new Review &amp; Pay, read the Terms &amp; Conditions control's state. | 4. Repeat for a changed search — new criteria, new results, a new offer.</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The new offer's Review &amp; Pay opens with Terms &amp; Conditions **not accepted**. Acceptance applies to the amount and offer that were on screen when it was given; it is not inherited by a different offer or a different price.</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Atomic, Negative, Validation</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Added 2026-10-04 from **DS-7 item 1**. **Covers `AC-37`** and story §4.9's rule that acceptance does not carry to a different offer or a changed price. The same principle as TC-RFLOW-038 (changing search criteria invalidates previous results) and TC-RFLOW-136 (a refresh does not restart the fare hold): a carried-over acceptance means the user agreed to one amount and was charged another. **Discovery: NOT EXECUTED.**</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Approved</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">TC-RFLOW-146</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">An insufficient wallet offers a top-up route rather than a dead end</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Verify the recovery path the workflow describes exists.</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Review &amp; Pay open with Wallet selected and a balance **below** the payable amount.</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">A low-balance wallet — **to be supplied (D-22, was OQ-11)**. Not held today.</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. Reach Review &amp; Pay with a wallet that cannot cover "Due Now". | 2. Read what the screen offers: the message, and whether a top-up action or link is presented. | 3. Read whether the Reissue context — booking, passengers, journey, selected offer — survives following it.</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The screen states the balance is insufficient **and offers a route to top up**. The user is not left at a dead end with the Reissue abandoned. Following the top-up route does not discard the selected offer or restart the Reissue from the Itinerary.</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Atomic, Negative, Recovery</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Added 2026-10-04 from **DS-7 item 3**, confirmed by the user. Covers no story AC — the story's AC-20 requires the balance be checked and the payment blocked, and stops there; the top-up loop appears only in the workflow diagrams (`Insufficient → Top up wallet → re-check balance`). Extends TC-RFLOW-056, which asserts the block but not the recovery. **Discovery: NOT TESTABLE** — needs the low-balance wallet of **D-22**, committed but not yet delivered. Declared Gap until it arrives.</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Approved</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">TC-RFLOW-147</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">After a top-up the balance is re-checked and the Reissue can continue</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Verify the loop closes — topping up returns the user to a payable state without restarting.</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">TC-RFLOW-146 executed; the wallet is below the payable amount. **A top-up is a financial action: the human performs it (§0.4, D-1). The platform never charges or credits a wallet.**</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">A low-balance wallet — **to be supplied (D-22)**. Not held today.</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. From the insufficient-balance state, the **human** tops the wallet up to cover the amount. | 2. Return to Review &amp; Pay and read the displayed balance. | 3. Read whether the Wallet payment method is now selectable and the payment action available. | 4. Confirm the selected offer, passengers, journey and amount are the same as before the top-up.</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The balance is **re-checked against the current figure**, not a cached one. With sufficient funds the Wallet method becomes selectable and the flow can continue, on the **same** offer and the same amount. The user never has to restart the Reissue from the Itinerary because of a top-up.</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">End-to-End, Positive, Recovery</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Added 2026-10-04 from **DS-7 item 3**. Covers no story AC. Pairs with TC-RFLOW-057, which requires the balance be revalidated immediately before payment — this is the same revalidation seen from the recovery side. **The top-up itself is human-performed and read-only for the platform.** **Discovery: NOT TESTABLE** — needs **D-22**'s wallet. Declared Gap.</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Approved</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">TC-RFLOW-148</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The Booking Confirmation displays Terms &amp; Conditions</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Verify the terms are presented again on the completed reissue, as the workflow describes.</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">A completed Reissue. **The human performed the payment (§0.4, D-1); this case is read-only.**</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">A booking reference produced by a human-performed exchange.</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. Open the reissue Booking Confirmation for the new booking reference. | 2. Locate the Terms &amp; Conditions on the confirmation and read whether content is reachable. | 3. Read it alongside the other confirmation elements — new booking and order information, PNR, segment and passenger details, fare details, and the E-ticket / Print / Search actions.</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Terms &amp; Conditions are displayed on the reissue confirmation and their content is reachable. They appear as information on a completed transaction, not as an acceptance control — nothing on the confirmation asks the user to agree to anything after the money has been taken.</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P3</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Atomic, Positive</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Added 2026-10-04 from **DS-7 item 1**, confirmed by the user. **Covers `AC-37`**'s second half (terms displayed on the Confirmation as information). AC-32 requires the confirmation follow "the agreed Reissue-specific UI", and no design was supplied (**D-23**: a screenshot of the current build is a regression baseline, not an oracle). **This case therefore asserts presence, not layout** — it can pass or fail honestly, which TC-RFLOW-092's design-conformance half cannot. The workflow diagram lists Terms &amp; Conditions and the E-ticket / Print / Search actions among the confirmation's elements. **Discovery: NOT EXECUTED** — runnable read-only on a booking the human has already exchanged.</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Approved</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Pending</t>
         </is>
